--- a/linkedin/Programacion_LinkedIn_Octubre_2026.xlsx
+++ b/linkedin/Programacion_LinkedIn_Octubre_2026.xlsx
@@ -359,7 +359,7 @@
     <t xml:space="preserve">PRIMER COMENTARIO · publícalo apenas salga el post: copia la celda de abajo</t>
   </si>
   <si>
-    <t xml:space="preserve">En el taller docente gratuito de CCA trabajamos este tipo de estrategias con el equipo del colegio. Si quieres llevarlo a tus docentes, aquí está la información: https://gimnasiodelcerebro.co/colegios.html</t>
+    <t xml:space="preserve">En el taller docente gratuito del Gimnasio del Cerebro trabajamos este tipo de estrategias con el equipo del colegio. Si quieres llevarlo a tus docentes, aquí está la información: https://gimnasiodelcerebro.co/colegios.html</t>
   </si>
   <si>
     <t xml:space="preserve">Referencias del post: Diamond (2013); maduración tardía de la corteza prefrontal (Casey, Giedd y colegas)</t>
